--- a/output/pdf_financials_xlsx/SOLR.xlsx
+++ b/output/pdf_financials_xlsx/SOLR.xlsx
@@ -3289,28 +3289,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>11.329225</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>12.519049</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>12.919692</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>13.826269</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>16.081231</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>16.751461</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>17.039615</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>17.417669</v>
       </c>
     </row>
     <row r="93">
@@ -5816,7 +5816,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -6898,7 +6902,11 @@
           <t>Reserves (notes 13 and 14)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -7516,7 +7524,11 @@
           <t>Reserves (notes 15 and 16)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -8640,7 +8652,11 @@
           <t>Reserves (notes 12 and 11)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -9584,7 +9600,11 @@
           <t>Reserve 9</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -10302,7 +10322,11 @@
           <t>Reserve 13</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>11.329225</v>
       </c>

--- a/output/pdf_financials_xlsx/SOLR.xlsx
+++ b/output/pdf_financials_xlsx/SOLR.xlsx
@@ -709,16 +709,16 @@
         <v>2.546334</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.812365</v>
+        <v>3.198054</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.374737</v>
+        <v>4.283008</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.467804</v>
+        <v>3.037881</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.593728</v>
+        <v>2.869308</v>
       </c>
     </row>
     <row r="11">
@@ -759,28 +759,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0162</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.08239200000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.010407</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00696</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.039567</v>
       </c>
     </row>
     <row r="13">
@@ -1266,28 +1266,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.187765</v>
+        <v>-3.203965</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.476999</v>
+        <v>-7.503999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.335673</v>
+        <v>-2.357273</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.764374</v>
+        <v>-2.785974</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.448864</v>
+        <v>-0.531256</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.746914</v>
+        <v>-2.757321</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.811861</v>
+        <v>-1.804901</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.684134</v>
+        <v>-0.644567</v>
       </c>
     </row>
     <row r="28">
@@ -1328,28 +1328,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.175884</v>
+        <v>-3.192084</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.449359</v>
+        <v>-7.476359</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.298228</v>
+        <v>-2.319828</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.690206</v>
+        <v>-2.711806</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.420892</v>
+        <v>-0.503284</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.715368</v>
+        <v>-2.725775</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.775042</v>
+        <v>-1.768082</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.659675</v>
+        <v>-0.620108</v>
       </c>
     </row>
     <row r="30">
@@ -1359,28 +1359,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-53.5360630642795</v>
+        <v>-53.80914741548418</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-161.8481520782222</v>
+        <v>-162.4347663233018</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-115.9029497349828</v>
+        <v>-116.9922688600982</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-122.0768353572788</v>
+        <v>-123.0570055166336</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-11.47976084331615</v>
+        <v>-13.7269892425314</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-56.2655823144047</v>
+        <v>-56.48122745537491</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-23.74975866133204</v>
+        <v>-23.65663505057643</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-12.11133524040085</v>
+        <v>-11.38490297988326</v>
       </c>
     </row>
     <row r="31">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.130526</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.179203</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.077888</v>
@@ -1471,16 +1471,16 @@
         <v>0.045634</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.169258</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.650061</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.7029879999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.009697000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.130526</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.179203</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.077888</v>
@@ -1533,16 +1533,16 @@
         <v>0.045634</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.169258</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.650061</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.7029879999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.009697000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.380658</v>
+        <v>0.250132</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.629804</v>
+        <v>0.450601</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.278825</v>
@@ -1905,16 +1905,16 @@
         <v>0.785349</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.178948</v>
+        <v>0.009690000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.178498</v>
+        <v>0.528437</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.711551</v>
+        <v>0.008562999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.14978</v>
+        <v>0.140083</v>
       </c>
     </row>
     <row r="49">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -21462,7 +21462,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E410" s="5" t="n">

--- a/output/pdf_financials_xlsx/SOLR.xlsx
+++ b/output/pdf_financials_xlsx/SOLR.xlsx
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002592</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -4397,13 +4397,13 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>0</v>
+        <v>-0.017245</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>-0.185026</v>
+        <v>-0.286717</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>-0.007385</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>-0.018711</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002592</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>-3.918369</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.746702</v>
+        <v>-1.749294</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.979106</v>
@@ -10436,7 +10436,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -14828,7 +14832,11 @@
           <t>Acquisition of equipment (note 5)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -15222,7 +15230,11 @@
           <t>Interest and financing fees paid</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -15278,7 +15290,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -17288,7 +17304,11 @@
           <t>Acquisition of equipment 5</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -17734,7 +17754,11 @@
           <t>Private placements 9</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -18126,7 +18150,11 @@
           <t>Interest and financing fees paid 7</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -19918,7 +19946,11 @@
           <t>Private placements 13</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E275" s="5" t="n">
         <v>0.916713</v>
       </c>
@@ -20252,7 +20284,11 @@
           <t>Interest and financing fees paid</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E281" s="5" t="n">
         <v>-0.017245</v>
       </c>
